--- a/Questões Arena do Conhecimento/22Q2_DDL_DML_Normalização.xlsx
+++ b/Questões Arena do Conhecimento/22Q2_DDL_DML_Normalização.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Nassau\2026.1\Projeto de Banco de Dados\Questões Arena do Conhecimento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projetos\arena_conhecimento\deploy_me\Questões Arena do Conhecimento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2E454B-E58C-4900-A71A-C8BA87EFFC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBEFB391-CFB3-4D62-91CE-16E46242C6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Duas Alternativas" sheetId="2" r:id="rId1"/>
